--- a/Night_plans/Lick-2026B-01/Lick_2026B-01_Night_plan.xlsx
+++ b/Night_plans/Lick-2026B-01/Lick_2026B-01_Night_plan.xlsx
@@ -73,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -82,6 +82,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -636,7 +637,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -644,7 +644,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
@@ -887,6 +886,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -906,6 +910,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -929,6 +936,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.0625</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -954,6 +964,16 @@
       </c>
       <c r="K4" t="n">
         <v>23.75</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>9 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3 x 1800</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1095,6 +1115,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -1114,6 +1139,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -1137,6 +1165,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.04166666666666666</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -1162,6 +1193,16 @@
       </c>
       <c r="K4" t="n">
         <v>22.64</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1303,6 +1344,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -1322,6 +1368,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -1345,6 +1394,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.02777777777777778</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -1370,6 +1422,16 @@
       </c>
       <c r="K4" t="n">
         <v>21.54</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1511,6 +1573,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -1530,6 +1597,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -1553,6 +1623,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.04166666666666666</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -1578,6 +1651,16 @@
       </c>
       <c r="K4" t="n">
         <v>20.99</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1988,6 +2071,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -2012,6 +2100,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -2035,6 +2126,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.02777777777777778</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -2060,6 +2154,16 @@
       </c>
       <c r="K4" t="n">
         <v>21.88</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2389,6 +2493,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -2408,6 +2517,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -2431,6 +2543,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.04166666666666666</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -2456,6 +2571,16 @@
       </c>
       <c r="K4" t="n">
         <v>23.08</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2597,6 +2722,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -2616,6 +2746,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -2639,6 +2772,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.04166666666666666</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -2664,6 +2800,16 @@
       </c>
       <c r="K4" t="n">
         <v>19.77</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -2805,6 +2951,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -2824,6 +2975,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -2847,6 +3001,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.02777777777777778</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -2872,6 +3029,16 @@
       </c>
       <c r="K4" t="n">
         <v>19.88</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3013,6 +3180,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -3032,6 +3204,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -3055,6 +3230,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.04166666666666666</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -3080,6 +3258,16 @@
       </c>
       <c r="K4" t="n">
         <v>20.84</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3221,6 +3409,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -3240,6 +3433,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -3263,6 +3459,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.04166666666666666</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -3288,6 +3487,16 @@
       </c>
       <c r="K4" t="n">
         <v>23.24</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3429,6 +3638,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -3448,6 +3662,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -3471,6 +3688,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.04166666666666666</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -3496,6 +3716,16 @@
       </c>
       <c r="K4" t="n">
         <v>22.38</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -3637,6 +3867,11 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Kast setup: d57 dichroic | red 600/7500 | blue 600/4310 | 2" slit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="Q2" s="2" t="inlineStr">
@@ -3656,6 +3891,9 @@
       </c>
     </row>
     <row r="3">
+      <c r="D3" s="6" t="n">
+        <v>0.003472222222222222</v>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">slew to --&gt; </t>
@@ -3679,6 +3917,9 @@
       </c>
     </row>
     <row r="4">
+      <c r="D4" s="6" t="n">
+        <v>0.02777777777777778</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Science + overhead</t>
@@ -3704,6 +3945,16 @@
       </c>
       <c r="K4" t="n">
         <v>21.27</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4 x 600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2 x 1200</t>
+        </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
